--- a/docs/user-stories.xlsx
+++ b/docs/user-stories.xlsx
@@ -669,6 +669,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
@@ -765,7 +766,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>As a Partner, I want to reassign the Associate or Paralegal on a consultation or case, so that staffing can be corrected after the fact.</t>
+          <t>As a Partner, I want to reassign the Associate or Paralegal on a consultation before its case is opened or on an open case, so that staffing can be corrected after the fact.</t>
         </is>
       </c>
     </row>
@@ -781,6 +782,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
@@ -841,10 +843,11 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>As an Associate, I want to close an active case with a final resolution status, so that completed cases are officially closed.</t>
-        </is>
-      </c>
-    </row>
+          <t>As an Associate, I want to close an active case with a final resolution status, so that completed cases are officially closed once all of their billing is settled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -969,6 +972,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
@@ -1045,6 +1049,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
@@ -1117,7 +1122,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>As a Finance Officer, I want to edit disputed pending charges, void incorrect invoices, and refund paid charges, so that billing errors can be corrected at any stage.</t>
+          <t>As a Finance Officer, I want to edit disputed pending charges, void incorrect invoices, and refund paid charges, so that billing errors can be corrected while the case is open.</t>
         </is>
       </c>
     </row>
@@ -1133,6 +1138,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>

--- a/docs/user-stories.xlsx
+++ b/docs/user-stories.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>As a Client, I want to submit a consultation request with legal issue details and track its status and consultation meeting, so that the firm can evaluate my legal matter and I know where it stands.</t>
+          <t>As a Client, I want to request a consultation with legal issue details and track its status and consultation meeting, so that the firm can evaluate my legal matter and I know where it stands.</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>As a Client Relations Officer, I want to submit walk-in clients' consultation requests and follow them and their scheduled consultation meetings, so that a Partner can perform a conflict check.</t>
+          <t>As a Client Relations Officer, I want to request consultations for walk-in clients and follow them and their scheduled consultation meetings, so that a Partner can perform a conflict check.</t>
         </is>
       </c>
     </row>
